--- a/credits.xlsx
+++ b/credits.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pokemon TCG Legacy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C88B4866-A71B-455D-8F03-55523550B232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A89E95-833F-4654-AB56-4270950BB424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="17685" xr2:uid="{7635DB46-9F12-4EC4-9ABF-7C966C934E56}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{7635DB46-9F12-4EC4-9ABF-7C966C934E56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>Credits</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>In Battle Trainer Sprites</t>
   </si>
@@ -47,17 +44,32 @@
     <t>https://eeveeexpo.com/resources/391/</t>
   </si>
   <si>
-    <t>Please credit if used to:</t>
-  </si>
-  <si>
     <t>Mr. Gela/theo#7722</t>
+  </si>
+  <si>
+    <t>original car sprite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">r/PokemonRMXP • 1y ago </t>
+  </si>
+  <si>
+    <t>New_Personality_9208</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Sprite</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -69,6 +81,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -91,17 +111,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -115,72 +135,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4EA0FD7-9930-6BF3-DFE7-1A9AE435210F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2971800" y="190500"/>
-          <a:ext cx="152400" cy="104775"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -500,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D8449EA-7B8C-4284-BC16-D53892B08179}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="44.5703125" customWidth="1"/>
@@ -509,30 +463,45 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" t="s">
-        <v>2</v>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
+      <c r="B4" s="1"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" display="https://www.reddit.com/r/PokemonRMXP/" xr:uid="{484AF3F9-A79A-44A4-BE84-81893A8B5A0F}"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://www.reddit.com/user/New_Personality_9208/" xr:uid="{B6FC823D-A351-4968-90C5-AB0A9D22DCC7}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/credits.xlsx
+++ b/credits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pokemon TCG Legacy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A89E95-833F-4654-AB56-4270950BB424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68643065-5D0E-4C7A-B8A3-5AE080410DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{7635DB46-9F12-4EC4-9ABF-7C966C934E56}"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="12645" xr2:uid="{7635DB46-9F12-4EC4-9ABF-7C966C934E56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>In Battle Trainer Sprites</t>
   </si>
@@ -63,22 +63,32 @@
   </si>
   <si>
     <t>Sprite</t>
+  </si>
+  <si>
+    <t>Gen 4 OW Sprites by:</t>
+  </si>
+  <si>
+    <t>Neo-Spriteman</t>
+  </si>
+  <si>
+    <t>VanillaSunshine</t>
+  </si>
+  <si>
+    <t>PurpleZaffre &amp; Maicerochico</t>
+  </si>
+  <si>
+    <t>AtomicReactor</t>
+  </si>
+  <si>
+    <t>https://eeveeexpo.com/resources/404/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -113,12 +123,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -454,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D8449EA-7B8C-4284-BC16-D53892B08179}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="44.5703125" customWidth="1"/>
@@ -487,15 +496,47 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="1"/>
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
